--- a/doctool/test/auto/scenario12/システム機能設計書_サンプル_S12.xlsx
+++ b/doctool/test/auto/scenario12/システム機能設計書_サンプル_S12.xlsx
@@ -2246,7 +2246,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>作成者</author>
-    <author>山田　太郎</author>
   </authors>
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
@@ -2284,64 +2283,10 @@
 08/02山田 済</t>
       </text>
     </comment>
-    <comment ref="E63" authorId="1" shapeId="0">
-      <text>
-        <t>山田　太郎:d
-機能・仕様誤りの指摘例（カテゴリd）。</t>
-      </text>
-    </comment>
-    <comment ref="E64" authorId="1" shapeId="0">
-      <text>
-        <t>山田　太郎:e
-設計・ドキュメント規約違反の指摘例（カテゴリe）。</t>
-      </text>
-    </comment>
-    <comment ref="E65" authorId="1" shapeId="0">
-      <text>
-        <t>山田　太郎:f
-記述誤りの指摘例（カテゴリf）。</t>
-      </text>
-    </comment>
-    <comment ref="E66" authorId="1" shapeId="0">
-      <text>
-        <t>山田　太郎:g
-疑問点・確認の指摘例（カテゴリg）。</t>
-      </text>
-    </comment>
-    <comment ref="E67" authorId="1" shapeId="0">
-      <text>
-        <t>山田　太郎:h
-改善要望の指摘例（カテゴリh）。</t>
-      </text>
-    </comment>
-    <comment ref="E68" authorId="1" shapeId="0">
-      <text>
-        <t>山田　太郎:i
-仕様変更の指摘例（カテゴリi）。</t>
-      </text>
-    </comment>
-    <comment ref="E69" authorId="1" shapeId="0">
-      <text>
-        <t>山田　太郎:j
-テスト項目漏れの指摘例（カテゴリj）。</t>
-      </text>
-    </comment>
-    <comment ref="E70" authorId="1" shapeId="0">
-      <text>
-        <t>山田　太郎:k
-テスト漏れの指摘例（カテゴリk）。</t>
-      </text>
-    </comment>
     <comment ref="A71" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:
 自動で挿入される名前とコロンの直後に何も書かれていない場合、日時コメント・指摘コメントとして扱われない。</t>
-      </text>
-    </comment>
-    <comment ref="E71" authorId="1" shapeId="0">
-      <text>
-        <t>山田　太郎:l
-その他の指摘例（カテゴリl）。</t>
       </text>
     </comment>
   </commentList>
@@ -3409,7 +3354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN33"/>
+  <dimension ref="A1:AN34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="4.83203125" defaultRowHeight="11.25"/>
   <sheetData>
     <row r="1" customFormat="1" s="11">
@@ -16646,6 +16591,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="E65" t="inlineStr">
         <is>
@@ -16653,6 +16599,7 @@
         </is>
       </c>
     </row>
+    <row r="66"/>
     <row r="70">
       <c r="A70" s="94" t="n"/>
     </row>
